--- a/voorspellingen.xlsx
+++ b/voorspellingen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cuccibu-my.sharepoint.com/personal/joris_wijnen_cuccibu_nl/Documents/Documents/Cuccipool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="334" documentId="11_F25DC773A252ABDACC104897891D529C5ADE58F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A72F0D7-DB7E-47A9-A371-5587EA5F53F4}"/>
+  <xr:revisionPtr revIDLastSave="1814" documentId="11_F25DC773A252ABDACC104897891D529C5ADE58F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9724869-0ADF-45AD-BDD3-085E1F281B2B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2436" uniqueCount="173">
   <si>
     <t>Joep</t>
   </si>
@@ -366,13 +366,184 @@
     <t>Jordy</t>
   </si>
   <si>
-    <t>2-0-</t>
-  </si>
-  <si>
     <t>O. Dembélé</t>
   </si>
   <si>
     <t>J. Bellingham</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>L. Martinez</t>
+  </si>
+  <si>
+    <t>Vinicius Jr.</t>
+  </si>
+  <si>
+    <t>Brazilië</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>C. Ronaldo</t>
+  </si>
+  <si>
+    <t>Evie</t>
+  </si>
+  <si>
+    <t>M. Depay</t>
+  </si>
+  <si>
+    <t>Neymar</t>
+  </si>
+  <si>
+    <t>M. Salah</t>
+  </si>
+  <si>
+    <t>Willemijn</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Job</t>
+  </si>
+  <si>
+    <t>M. Olise</t>
+  </si>
+  <si>
+    <t>M. Oyarzabal</t>
+  </si>
+  <si>
+    <t>G. Ramos</t>
+  </si>
+  <si>
+    <t>D. Undav</t>
+  </si>
+  <si>
+    <t>Nynke</t>
+  </si>
+  <si>
+    <t>R. Lukaku</t>
+  </si>
+  <si>
+    <t>B. Fernandes</t>
+  </si>
+  <si>
+    <t>Britt</t>
+  </si>
+  <si>
+    <t>Nederland</t>
+  </si>
+  <si>
+    <t>Tim</t>
+  </si>
+  <si>
+    <t>6-3</t>
+  </si>
+  <si>
+    <t>7-7</t>
+  </si>
+  <si>
+    <t>7-0</t>
+  </si>
+  <si>
+    <t>10-0</t>
+  </si>
+  <si>
+    <t>D. Dumfries</t>
+  </si>
+  <si>
+    <t>Ashwin</t>
+  </si>
+  <si>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>M. Cunha</t>
+  </si>
+  <si>
+    <t>Raphinha</t>
+  </si>
+  <si>
+    <t>F. Torres</t>
+  </si>
+  <si>
+    <t>Cyrille</t>
+  </si>
+  <si>
+    <t>Gijs</t>
+  </si>
+  <si>
+    <t>Dennis</t>
+  </si>
+  <si>
+    <t>Kris</t>
+  </si>
+  <si>
+    <t>D. Malen</t>
+  </si>
+  <si>
+    <t>Sana</t>
+  </si>
+  <si>
+    <t>E. Džeko</t>
+  </si>
+  <si>
+    <t>R. Jiménez</t>
+  </si>
+  <si>
+    <t>B. Díaz</t>
+  </si>
+  <si>
+    <t>Marokko</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>Lau</t>
+  </si>
+  <si>
+    <t>Badr</t>
+  </si>
+  <si>
+    <t>J. Álvarez</t>
+  </si>
+  <si>
+    <t>Luc</t>
+  </si>
+  <si>
+    <t>L. Paquetá</t>
   </si>
 </sst>
 </file>
@@ -715,7 +886,7 @@
     <col min="2" max="23" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -725,8 +896,62 @@
       <c r="D1" s="2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -739,8 +964,62 @@
       <c r="D2" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -753,8 +1032,62 @@
       <c r="D3" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -767,8 +1100,62 @@
       <c r="D4" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -781,8 +1168,62 @@
       <c r="D5" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -795,8 +1236,62 @@
       <c r="D6" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -809,8 +1304,62 @@
       <c r="D7" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -823,8 +1372,62 @@
       <c r="D8" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -837,8 +1440,62 @@
       <c r="D9" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -851,8 +1508,62 @@
       <c r="D10" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -865,8 +1576,62 @@
       <c r="D11" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -879,8 +1644,62 @@
       <c r="D12" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -893,8 +1712,62 @@
       <c r="D13" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -907,8 +1780,62 @@
       <c r="D14" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -921,8 +1848,62 @@
       <c r="D15" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>57</v>
       </c>
@@ -934,6 +1915,60 @@
       </c>
       <c r="D16" s="2" t="s">
         <v>84</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -949,6 +1984,60 @@
       <c r="D17" s="2" t="s">
         <v>88</v>
       </c>
+      <c r="E17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -963,6 +2052,60 @@
       <c r="D18" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="E18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -977,6 +2120,60 @@
       <c r="D19" s="2" t="s">
         <v>84</v>
       </c>
+      <c r="E19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -991,6 +2188,60 @@
       <c r="D20" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="E20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -1005,6 +2256,60 @@
       <c r="D21" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="E21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -1019,6 +2324,60 @@
       <c r="D22" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="E22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1033,6 +2392,60 @@
       <c r="D23" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -1047,6 +2460,60 @@
       <c r="D24" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="E24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="25" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
@@ -1061,24 +2528,60 @@
       <c r="D25" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
+      <c r="E25" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="V25" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="W25" s="3"/>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
@@ -1094,6 +2597,60 @@
       <c r="D26" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="E26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -1108,6 +2665,60 @@
       <c r="D27" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="E27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -1122,6 +2733,60 @@
       <c r="D28" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1136,6 +2801,60 @@
       <c r="D29" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1150,6 +2869,60 @@
       <c r="D30" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="E30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -1164,6 +2937,60 @@
       <c r="D31" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="E31" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="U31" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -1178,8 +3005,62 @@
       <c r="D32" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="T32" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="U32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -1192,8 +3073,62 @@
       <c r="D33" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -1206,8 +3141,62 @@
       <c r="D34" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>54</v>
       </c>
@@ -1220,8 +3209,62 @@
       <c r="D35" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -1234,8 +3277,62 @@
       <c r="D36" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E36" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T36" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U36" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>68</v>
       </c>
@@ -1248,8 +3345,62 @@
       <c r="D37" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>58</v>
       </c>
@@ -1262,8 +3413,62 @@
       <c r="D38" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>31</v>
       </c>
@@ -1276,8 +3481,62 @@
       <c r="D39" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E39" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T39" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="U39" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1290,8 +3549,62 @@
       <c r="D40" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E40" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T40" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -1304,8 +3617,62 @@
       <c r="D41" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="S41" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T41" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U41" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>62</v>
       </c>
@@ -1318,8 +3685,62 @@
       <c r="D42" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E42" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>60</v>
       </c>
@@ -1332,8 +3753,62 @@
       <c r="D43" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="T43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>71</v>
       </c>
@@ -1346,8 +3821,62 @@
       <c r="D44" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>33</v>
       </c>
@@ -1360,8 +3889,62 @@
       <c r="D45" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E45" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U45" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>65</v>
       </c>
@@ -1374,8 +3957,62 @@
       <c r="D46" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E46" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U46" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>34</v>
       </c>
@@ -1388,8 +4025,62 @@
       <c r="D47" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E47" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="U47" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="V47" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>35</v>
       </c>
@@ -1400,6 +4091,60 @@
         <v>93</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="R48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="T48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="U48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V48" s="2" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1416,24 +4161,60 @@
       <c r="D49" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
+      <c r="E49" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="W49" s="3"/>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.3">
@@ -1449,6 +4230,60 @@
       <c r="D50" s="2" t="s">
         <v>88</v>
       </c>
+      <c r="E50" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S50" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T50" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U50" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
@@ -1463,6 +4298,60 @@
       <c r="D51" s="2" t="s">
         <v>84</v>
       </c>
+      <c r="E51" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="T51" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U51" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -1477,6 +4366,60 @@
       <c r="D52" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="E52" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R52" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -1491,6 +4434,60 @@
       <c r="D53" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="E53" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R53" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S53" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T53" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U53" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="V53" s="2" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
@@ -1505,6 +4502,60 @@
       <c r="D54" s="2" t="s">
         <v>85</v>
       </c>
+      <c r="E54" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R54" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S54" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="T54" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="U54" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
@@ -1519,6 +4570,60 @@
       <c r="D55" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E55" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="T55" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U55" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -1533,6 +4638,60 @@
       <c r="D56" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="E56" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="R56" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S56" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="T56" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="U56" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="V56" s="2" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -1547,6 +4706,60 @@
       <c r="D57" s="2" t="s">
         <v>91</v>
       </c>
+      <c r="E57" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T57" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="U57" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
@@ -1561,6 +4774,60 @@
       <c r="D58" s="2" t="s">
         <v>85</v>
       </c>
+      <c r="E58" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="R58" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T58" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="U58" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
@@ -1575,6 +4842,60 @@
       <c r="D59" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E59" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T59" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="U59" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -1589,6 +4910,60 @@
       <c r="D60" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="E60" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q60" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R60" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="S60" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T60" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="U60" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -1603,6 +4978,60 @@
       <c r="D61" s="2" t="s">
         <v>85</v>
       </c>
+      <c r="E61" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q61" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R61" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S61" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T61" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="U61" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -1617,6 +5046,60 @@
       <c r="D62" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E62" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q62" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="R62" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S62" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T62" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
@@ -1631,6 +5114,60 @@
       <c r="D63" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="E63" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q63" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R63" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="S63" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T63" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U63" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -1645,6 +5182,60 @@
       <c r="D64" s="2" t="s">
         <v>91</v>
       </c>
+      <c r="E64" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q64" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R64" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S64" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="U64" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -1659,6 +5250,60 @@
       <c r="D65" s="2" t="s">
         <v>84</v>
       </c>
+      <c r="E65" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q65" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="R65" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S65" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="U65" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -1673,6 +5318,60 @@
       <c r="D66" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E66" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q66" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R66" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S66" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U66" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
@@ -1687,6 +5386,60 @@
       <c r="D67" s="2" t="s">
         <v>84</v>
       </c>
+      <c r="E67" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q67" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R67" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S67" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T67" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="U67" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -1701,6 +5454,60 @@
       <c r="D68" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E68" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q68" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R68" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S68" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T68" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U68" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -1715,6 +5522,60 @@
       <c r="D69" s="2" t="s">
         <v>84</v>
       </c>
+      <c r="E69" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q69" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R69" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S69" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T69" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="U69" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="V69" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -1729,6 +5590,60 @@
       <c r="D70" s="2" t="s">
         <v>85</v>
       </c>
+      <c r="E70" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q70" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="R70" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S70" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T70" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U70" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
@@ -1743,6 +5658,60 @@
       <c r="D71" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E71" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q71" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R71" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S71" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T71" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U71" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="V71" s="2" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -1757,6 +5726,60 @@
       <c r="D72" s="2" t="s">
         <v>84</v>
       </c>
+      <c r="E72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q72" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="R72" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="S72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T72" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="V72" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="73" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
@@ -1771,24 +5794,60 @@
       <c r="D73" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
-      <c r="P73" s="3"/>
-      <c r="Q73" s="3"/>
-      <c r="R73" s="3"/>
-      <c r="S73" s="3"/>
-      <c r="T73" s="3"/>
-      <c r="U73" s="3"/>
-      <c r="V73" s="3"/>
+      <c r="E73" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N73" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="P73" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q73" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R73" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="S73" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="T73" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="U73" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V73" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="W73" s="3"/>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.3">
@@ -1802,7 +5861,61 @@
         <v>102</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q74" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="R74" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="T74" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="U74" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.3">
@@ -1818,6 +5931,60 @@
       <c r="D75" s="2" t="s">
         <v>102</v>
       </c>
+      <c r="E75" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q75" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R75" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="S75" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T75" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="U75" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="V75" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -1832,6 +5999,60 @@
       <c r="D76" s="2" t="s">
         <v>74</v>
       </c>
+      <c r="E76" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q76" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="R76" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="S76" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="T76" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="U76" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="V76" s="2" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -1846,6 +6067,60 @@
       <c r="D77" s="2" t="s">
         <v>103</v>
       </c>
+      <c r="E77" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q77" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="R77" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="S77" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="T77" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="U77" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="V77" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -1860,6 +6135,60 @@
       <c r="D78" s="2" t="s">
         <v>105</v>
       </c>
+      <c r="E78" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q78" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="R78" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="S78" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="T78" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="U78" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="79" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
@@ -1872,26 +6201,62 @@
         <v>77</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
-      <c r="L79" s="3"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3"/>
-      <c r="O79" s="3"/>
-      <c r="P79" s="3"/>
-      <c r="Q79" s="3"/>
-      <c r="R79" s="3"/>
-      <c r="S79" s="3"/>
-      <c r="T79" s="3"/>
-      <c r="U79" s="3"/>
-      <c r="V79" s="3"/>
+        <v>114</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N79" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="P79" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q79" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="R79" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="S79" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="T79" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="U79" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="V79" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="W79" s="3"/>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.3">
@@ -1905,6 +6270,60 @@
         <v>81</v>
       </c>
       <c r="D80" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="V80" s="2" t="s">
         <v>80</v>
       </c>
     </row>

--- a/voorspellingen.xlsx
+++ b/voorspellingen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cuccibu-my.sharepoint.com/personal/joris_wijnen_cuccibu_nl/Documents/Documents/Cuccipool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1814" documentId="11_F25DC773A252ABDACC104897891D529C5ADE58F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9724869-0ADF-45AD-BDD3-085E1F281B2B}"/>
+  <xr:revisionPtr revIDLastSave="1815" documentId="11_F25DC773A252ABDACC104897891D529C5ADE58F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C219A96-933E-4A1E-8EB9-D4D6C8D1B20A}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2436" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="173">
   <si>
     <t>Joep</t>
   </si>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>83</v>
